--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -19577,6 +19577,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="836">
+      <c r="A836" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B836" t="n">
+        <v>0</v>
+      </c>
+      <c r="C836" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D836" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E836" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F836" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G836" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -19600,6 +19600,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="837">
+      <c r="A837" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B837" t="n">
+        <v>0</v>
+      </c>
+      <c r="C837" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D837" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E837" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F837" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G837" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B838" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C838" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D838" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="E838" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="F838" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G838" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -19646,6 +19646,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="839">
+      <c r="A839" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B839" t="n">
+        <v>0</v>
+      </c>
+      <c r="C839" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D839" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E839" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="F839" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G839" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B840" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C840" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D840" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E840" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F840" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G840" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -19510,22 +19510,22 @@
     </row>
     <row r="833">
       <c r="A833" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B833" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="C833" t="n">
-        <v>1.03999996185303</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="D833" t="n">
-        <v>0.995000004768372</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="E833" t="n">
-        <v>0.995000004768372</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="F833" t="n">
-        <v>1.03999996185303</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="G833" t="s">
         <v>7</v>
@@ -19533,19 +19533,19 @@
     </row>
     <row r="834">
       <c r="A834" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B834" t="n">
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="C834" t="n">
         <v>1.03999996185303</v>
       </c>
       <c r="D834" t="n">
-        <v>1.01999998092651</v>
+        <v>0.995000004768372</v>
       </c>
       <c r="E834" t="n">
-        <v>1.01999998092651</v>
+        <v>0.995000004768372</v>
       </c>
       <c r="F834" t="n">
         <v>1.03999996185303</v>
@@ -19556,22 +19556,22 @@
     </row>
     <row r="835">
       <c r="A835" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B835" t="n">
-        <v>2200</v>
+        <v>5500</v>
       </c>
       <c r="C835" t="n">
-        <v>1.04999995231628</v>
+        <v>1.03999996185303</v>
       </c>
       <c r="D835" t="n">
         <v>1.01999998092651</v>
       </c>
       <c r="E835" t="n">
-        <v>1.04999995231628</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="F835" t="n">
-        <v>1.01999998092651</v>
+        <v>1.03999996185303</v>
       </c>
       <c r="G835" t="s">
         <v>7</v>
@@ -19579,19 +19579,19 @@
     </row>
     <row r="836">
       <c r="A836" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B836" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="C836" t="n">
-        <v>1.01999998092651</v>
+        <v>1.04999995231628</v>
       </c>
       <c r="D836" t="n">
         <v>1.01999998092651</v>
       </c>
       <c r="E836" t="n">
-        <v>1.01999998092651</v>
+        <v>1.04999995231628</v>
       </c>
       <c r="F836" t="n">
         <v>1.01999998092651</v>
@@ -19602,7 +19602,7 @@
     </row>
     <row r="837">
       <c r="A837" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B837" t="n">
         <v>0</v>
@@ -19625,22 +19625,22 @@
     </row>
     <row r="838">
       <c r="A838" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B838" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="C838" t="n">
-        <v>1.03999996185303</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="D838" t="n">
-        <v>1.02999997138977</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="E838" t="n">
-        <v>1.02999997138977</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="F838" t="n">
-        <v>1.03999996185303</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="G838" t="s">
         <v>7</v>
@@ -19648,19 +19648,19 @@
     </row>
     <row r="839">
       <c r="A839" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B839" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="C839" t="n">
         <v>1.03999996185303</v>
       </c>
       <c r="D839" t="n">
-        <v>1.03999996185303</v>
+        <v>1.02999997138977</v>
       </c>
       <c r="E839" t="n">
-        <v>1.03999996185303</v>
+        <v>1.02999997138977</v>
       </c>
       <c r="F839" t="n">
         <v>1.03999996185303</v>
@@ -19671,22 +19671,22 @@
     </row>
     <row r="840">
       <c r="A840" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B840" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="C840" t="n">
-        <v>1.01999998092651</v>
+        <v>1.03999996185303</v>
       </c>
       <c r="D840" t="n">
-        <v>1.01999998092651</v>
+        <v>1.03999996185303</v>
       </c>
       <c r="E840" t="n">
-        <v>1.01999998092651</v>
+        <v>1.03999996185303</v>
       </c>
       <c r="F840" t="n">
-        <v>1.01999998092651</v>
+        <v>1.03999996185303</v>
       </c>
       <c r="G840" t="s">
         <v>7</v>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -19692,6 +19692,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="841">
+      <c r="A841" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B841" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C841" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D841" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E841" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F841" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G841" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B842" t="n">
+        <v>0</v>
+      </c>
+      <c r="C842" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D842" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E842" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F842" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G842" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -19738,6 +19738,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="843">
+      <c r="A843" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B843" t="n">
+        <v>0</v>
+      </c>
+      <c r="C843" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D843" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E843" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F843" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G843" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -22345,6 +22345,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="846">
+      <c r="A846" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B846" t="n">
+        <v>16500</v>
+      </c>
+      <c r="C846" t="n">
+        <v>1</v>
+      </c>
+      <c r="D846" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="E846" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="F846" t="n">
+        <v>1</v>
+      </c>
+      <c r="G846" t="n">
+        <v>1</v>
+      </c>
+      <c r="H846" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -22371,6 +22371,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="847">
+      <c r="A847" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B847" t="n">
+        <v>19800</v>
+      </c>
+      <c r="C847" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="D847" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="E847" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="F847" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="G847" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="H847" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -22449,6 +22449,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="850">
+      <c r="A850" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B850" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C850" t="n">
+        <v>0.964999973773956</v>
+      </c>
+      <c r="D850" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="E850" t="n">
+        <v>0.964999973773956</v>
+      </c>
+      <c r="F850" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="G850" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="H850" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -19984,7 +19984,9 @@
       <c r="E853" t="n">
         <v>0.985000014305115</v>
       </c>
-      <c r="F853"/>
+      <c r="F853" t="n">
+        <v>0.985000014305115</v>
+      </c>
       <c r="G853" t="s">
         <v>7</v>
       </c>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -19991,6 +19991,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="854">
+      <c r="A854" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B854" t="n">
+        <v>0</v>
+      </c>
+      <c r="C854" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="D854" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="E854" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="F854" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="G854" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B855" t="n">
+        <v>14300</v>
+      </c>
+      <c r="C855" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="D855" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E855" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F855"/>
+      <c r="G855" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -20030,8 +20030,31 @@
       <c r="E855" t="n">
         <v>0.959999978542328</v>
       </c>
-      <c r="F855"/>
+      <c r="F855" t="n">
+        <v>0.949999988079071</v>
+      </c>
       <c r="G855" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B856" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C856" t="n">
+        <v>0.995000004768372</v>
+      </c>
+      <c r="D856" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E856" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F856"/>
+      <c r="G856" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -20053,8 +20053,31 @@
       <c r="E856" t="n">
         <v>0.949999988079071</v>
       </c>
-      <c r="F856"/>
+      <c r="F856" t="n">
+        <v>0.964999973773956</v>
+      </c>
       <c r="G856" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B857" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C857" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="D857" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="E857" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="F857"/>
+      <c r="G857" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -20083,6 +20083,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="858">
+      <c r="A858" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B858" t="n">
+        <v>12100</v>
+      </c>
+      <c r="C858" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="D858" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="E858" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="F858" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="G858" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -22735,6 +22735,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="861">
+      <c r="A861" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B861" t="n">
+        <v>8800</v>
+      </c>
+      <c r="C861" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="D861" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E861" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="F861" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="G861" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="H861" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -22761,6 +22761,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="862">
+      <c r="A862" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B862" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C862" t="n">
+        <v>0.954999983310699</v>
+      </c>
+      <c r="D862" t="n">
+        <v>0.954999983310699</v>
+      </c>
+      <c r="E862" t="n">
+        <v>0.954999983310699</v>
+      </c>
+      <c r="F862" t="n">
+        <v>0.954999983310699</v>
+      </c>
+      <c r="G862" t="n">
+        <v>0.954999983310699</v>
+      </c>
+      <c r="H862" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -25376,6 +25376,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="863">
+      <c r="A863" t="s">
+        <v>9</v>
+      </c>
+      <c r="B863" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C863" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="D863" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="E863" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="F863" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="G863" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="H863" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I863" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -25405,6 +25405,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="864">
+      <c r="A864" t="s">
+        <v>9</v>
+      </c>
+      <c r="B864" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C864" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="D864" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="E864" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="F864" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="G864" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="H864" t="n">
+        <v>0</v>
+      </c>
+      <c r="I864" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -25434,6 +25434,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="865">
+      <c r="A865" t="s">
+        <v>9</v>
+      </c>
+      <c r="B865" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C865" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="D865" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="E865" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="F865" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="G865" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="H865" t="n">
+        <v>0</v>
+      </c>
+      <c r="I865" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="s">
+        <v>9</v>
+      </c>
+      <c r="B866" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C866" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="D866" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="E866" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="F866" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="G866" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="H866" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I866" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -25492,6 +25492,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="867">
+      <c r="A867" t="s">
+        <v>9</v>
+      </c>
+      <c r="B867" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C867" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="D867" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="E867" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="F867" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="G867" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="H867" t="n">
+        <v>0</v>
+      </c>
+      <c r="I867" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -25521,6 +25521,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="868">
+      <c r="A868" t="s">
+        <v>9</v>
+      </c>
+      <c r="B868" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C868" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="D868" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="E868" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="F868" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="G868" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="H868" t="n">
+        <v>0</v>
+      </c>
+      <c r="I868" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -25550,6 +25550,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="869">
+      <c r="A869" t="s">
+        <v>9</v>
+      </c>
+      <c r="B869" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C869" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="D869" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="E869" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="F869" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="G869" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="H869" t="n">
+        <v>0</v>
+      </c>
+      <c r="I869" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="s">
+        <v>9</v>
+      </c>
+      <c r="B870" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C870" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="D870" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="E870" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="F870" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="G870" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="H870" t="n">
+        <v>4400</v>
+      </c>
+      <c r="I870" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PSQ.MI.xlsx
+++ b/data/PSQ.MI.xlsx
@@ -25608,6 +25608,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="871">
+      <c r="A871" t="s">
+        <v>9</v>
+      </c>
+      <c r="B871" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C871" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="D871" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="E871" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="F871" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="G871" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="H871" t="n">
+        <v>0</v>
+      </c>
+      <c r="I871" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="s">
+        <v>9</v>
+      </c>
+      <c r="B872" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C872" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="D872" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="E872" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F872" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="G872" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="H872" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I872" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
